--- a/www/download/COUNTRY.WWW.rpA2.xlsx
+++ b/www/download/COUNTRY.WWW.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>Mundo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.783</t>
+          <t>83.0017362664145</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.922</t>
+          <t>86.4134594660474</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>102.014179313123</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6.672</t>
+          <t>290.539030642119</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.922</t>
+          <t>230.146087474519</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.098</t>
+          <t>245.732551893607</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.958</t>
+          <t>291.041461900099</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7.077</t>
+          <t>267.002405200733</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7.851</t>
+          <t>245.713826288875</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8.707</t>
+          <t>262.224648142049</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9.294</t>
+          <t>281.057814717828</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9.845</t>
+          <t>257.596762257753</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>10.986</t>
+          <t>256.04215086888</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>8.495</t>
+          <t>272.172645278223</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8.363</t>
+          <t>294.740221540565</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2660.653</t>
+          <t>0.918832633984032</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2706.543</t>
+          <t>0.977160857185607</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2747.777</t>
+          <t>0.989211529152815</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2779.313</t>
+          <t>0.945683298408303</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2813.91</t>
+          <t>0.913483438623916</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2881.293</t>
+          <t>0.841503316342954</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2937.735</t>
+          <t>0.831427417303781</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2954.355</t>
+          <t>0.823959192412664</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3027.326</t>
+          <t>0.839756615158129</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3086.349</t>
+          <t>0.825973966077634</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3143.524</t>
+          <t>0.818251328516197</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3193.889</t>
+          <t>0.828091022215457</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3225.066</t>
+          <t>0.931421651319746</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3270.744</t>
+          <t>0.974442819156062</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3280.621</t>
+          <t>0.948802629524249</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1340.302</t>
+          <t>0.557953052108528</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1366.883</t>
+          <t>0.609837517789126</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1397.427</t>
+          <t>0.623089564219576</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1415.446</t>
+          <t>0.60626869629476</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1441.207</t>
+          <t>0.593514958812601</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1481.326</t>
+          <t>0.560102937486231</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1514.24</t>
+          <t>0.566845337231621</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1528.087</t>
+          <t>0.582042038295091</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1560.787</t>
+          <t>0.607100839765454</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1599.028</t>
+          <t>0.623303979891331</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1636.236</t>
+          <t>0.62287878913123</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1673.185</t>
+          <t>0.633754582559104</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1700.913</t>
+          <t>0.720732596404075</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1735.034</t>
+          <t>0.733990505805978</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1740.403</t>
+          <t>0.757247082047407</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5050806.142</t>
+          <t>0.0485012496005905</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5155267.84</t>
+          <t>0.0842186942804708</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5214922.674</t>
+          <t>0.108043550192051</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5240263.707</t>
+          <t>0.138444981521225</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5294293.575</t>
+          <t>0.174847042228764</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5443795.236</t>
+          <t>0.193868487009157</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5634934.236</t>
+          <t>0.221597392815757</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5731499.926</t>
+          <t>0.254811152580188</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5933322.875</t>
+          <t>0.19587566198125</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6103273.608</t>
+          <t>0.256021129815599</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6167087.164</t>
+          <t>0.244521875061225</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6238229.391</t>
+          <t>0.238620123526547</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6308545.275</t>
+          <t>0.267262511207787</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6459964.684</t>
+          <t>0.246173366566948</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6489569.767</t>
+          <t>0.289335585757541</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2540163.195</t>
+          <t>12650256647199.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2598384.756</t>
+          <t>13004972065639.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2647332.327</t>
+          <t>13232813203751.9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2665359.155</t>
+          <t>13270629119300.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2706491.456</t>
+          <t>13377628968757.6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2788332.154</t>
+          <t>13874594382606.8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2876310.617</t>
+          <t>14237586366494.4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2925557.023</t>
+          <t>14538115762958.7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3011822.532</t>
+          <t>15311439532364.9</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3110191.477</t>
+          <t>16010068820911.5</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3156833.451</t>
+          <t>16545559337939.7</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3215874.427</t>
+          <t>17423487365980.6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3270922.466</t>
+          <t>17724434091115</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3356370.108</t>
+          <t>18211445181621</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3371243.035</t>
+          <t>18317903681412.6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>3763194167400.86</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>3749544115210.12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>3795961601114.17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>3853920145352.32</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>3933919494171.28</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>4149537480855.06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>4281703679803.06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>4340942504211.43</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4510801758824.33</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>4642986000831.68</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>4763031699463.83</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>4867400419142.14</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>4761877896386.33</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>4881306754480.28</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>4886466876530.36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>384178012.561611</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>353776472.335316</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>340952514.646113</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>364443040.708422</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>368118092.316633</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>353339371.857031</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>346065482.74496</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>324180856.896607</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>286518144.098807</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>255651936.250759</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>227540323.596278</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>202568518.812846</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>170300715.852923</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>152774946.623182</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>162281011.545621</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>30066520.6929297</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>30727355.2045012</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>30764208.5893888</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>30708896.2451452</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>28.17</t>
+          <t>32188409.8910965</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>33722599.7614167</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>33595983.6338188</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>34806746.049177</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>38829681.0110233</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>43806170.5567152</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>47608339.6011572</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>51207193.2951265</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>58332265.4137705</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>65942786.2254791</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>61677414.5269594</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>33.54</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34.19</t>
+          <t>56060688.4328249</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>34.69</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>35.23</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>87525633.878685</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>122789481.799158</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>0.491416474503729</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>0.545229787167991</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>0.567606813671574</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.83</t>
+          <t>0.567252599146969</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>0.57141677598991</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>0.549639710220851</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>0.562044717010826</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.57979855096648</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>0.580318894152746</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.60639268193036</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>0.603365489637898</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>45.47</t>
+          <t>0.61198168720255</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>0.692061608672368</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>0.707200816665042</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>0.724424337773727</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>6782647.33020936</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>6921569.83571776</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>6799923.18790552</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>6672392.99758787</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>6921926.22014192</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>7097527.55120248</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>6957930.10248792</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.21</t>
+          <t>7076765.80994838</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>7851414.30481901</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>8707490.97895034</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>9293630.10720785</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>9845214.4705543</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>10985641.7858809</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>8495405.66030324</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>8363000.72243344</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>83.0017362664145</t>
+          <t>2807.72079718313</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>86.4134594660474</t>
+          <t>2743.13396599043</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>102.014179313123</t>
+          <t>2716.39290757273</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>290.539030642119</t>
+          <t>2722.76028857489</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>230.146087474519</t>
+          <t>2729.60006449399</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>245.732551893607</t>
+          <t>2801.23101308007</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>291.041461900099</t>
+          <t>2827.62495324198</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>267.002405200733</t>
+          <t>2840.76912050754</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>245.713826288875</t>
+          <t>2890.0818688873</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>262.224648142049</t>
+          <t>2903.62937032633</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>281.057814717828</t>
+          <t>2910.96866404989</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>257.596762257753</t>
+          <t>2909.06292841991</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>256.04215086888</t>
+          <t>2799.60102459536</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>272.172645278223</t>
+          <t>2813.37802832447</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>294.740221540565</t>
+          <t>2807.66322917384</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15.221</t>
+          <t>1.3887882232666e-05</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.429</t>
+          <t>3.02791595458984e-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15.319</t>
+          <t>-5.57005405426025e-05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15.331</t>
+          <t>1.5556812286377e-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>-1.02221965789795e-05</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>16.435</t>
+          <t>-8.36849212646484e-05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16.416</t>
+          <t>-8.82148742675781e-06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16.947</t>
+          <t>-7.74860382080078e-06</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18.855</t>
+          <t>-8.10623168945312e-06</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>20.892</t>
+          <t>5.7518482208252e-05</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22.393</t>
+          <t>1.99079513549805e-05</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>24.078</t>
+          <t>-8.13007354736328e-05</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>26.916</t>
+          <t>9.77516174316406e-06</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>-7.74860382080078e-07</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>1.00135803222656e-05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17.578</t>
+          <t>4.15444374084473e-05</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.826</t>
+          <t>3.814697265625e-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17.622</t>
+          <t>4.56571578979492e-05</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17.526</t>
+          <t>-2.71201133728027e-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18.139</t>
+          <t>-5.88893890380859e-05</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18.643</t>
+          <t>-1.57952308654785e-06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18.571</t>
+          <t>-5.47170639038086e-05</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>1.18017196655273e-05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21.446</t>
+          <t>-3.7848949432373e-05</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>23.768</t>
+          <t>-8.04662704467773e-05</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>25.436</t>
+          <t>4.88758087158203e-06</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>27.318</t>
+          <t>-2.09808349609375e-05</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>30.664</t>
+          <t>1.60336494445801e-05</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>33.891</t>
+          <t>2.13384628295898e-05</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>32.314</t>
+          <t>7.4923038482666e-05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>96.778</t>
+          <t>2.3767352104187e-06</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>96.784</t>
+          <t>-3.56137752532959e-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>93.417</t>
+          <t>-2.38418579101562e-06</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>91.398</t>
+          <t>-8.64267349243164e-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>93.05</t>
+          <t>-1.89244747161865e-06</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>93.252</t>
+          <t>-1.12131237983704e-06</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>91.585</t>
+          <t>8.13975930213928e-06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>94.372</t>
+          <t>7.51391053199768e-06</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>105.628</t>
+          <t>-2.6114284992218e-06</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>117.888</t>
+          <t>1.10268592834473e-06</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>125.897</t>
+          <t>-2.62260437011719e-06</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>133.12</t>
+          <t>5.0663948059082e-07</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>146.41</t>
+          <t>-1.64955854415894e-05</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>104.856</t>
+          <t>-5.17070293426514e-06</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>102.58</t>
+          <t>2.01165676116943e-07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>4187.48105272566</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>4238.77231444069</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>4258.23603052016</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>4267.25313912314</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>4289.339333089</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>4340.89881537107</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>4416.87661989962</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>4487.84294020813</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>4567.25098305088</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>4664.36897153028</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>4667.34669735493</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>4689.35616753272</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>4737.09741331763</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>4803.00126754303</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>4841.60280465974</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>28.493</t>
+          <t>3828.78514994946</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>29.147</t>
+          <t>3889.27379595574</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29.078</t>
+          <t>3917.3168668575</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>28.869</t>
+          <t>3923.38301020762</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29.949</t>
+          <t>3949.94134678411</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30.886</t>
+          <t>4011.34258697465</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30.695</t>
+          <t>4117.63311100096</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>31.979</t>
+          <t>4204.52522937324</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>35.759</t>
+          <t>4293.31770701111</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>4399.8403561797</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>43.347</t>
+          <t>4408.60522939966</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>46.869</t>
+          <t>4429.98845929924</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>52.756</t>
+          <t>4484.36142583276</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>58.372</t>
+          <t>4580.76468932364</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>55.504</t>
+          <t>4629.30602252108</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>5508610.12112343</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>97.72</t>
+          <t>5779500.38561317</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>98.92</t>
+          <t>5835243.83024285</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>94.57</t>
+          <t>5825939.74977636</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>91.35</t>
+          <t>6156193.03397744</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>6918403.94604327</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>6759373.98424006</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>7066389.67821914</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>83.98</t>
+          <t>8247724.71966098</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>10000629.7768033</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>81.83</t>
+          <t>11347033.5735735</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>82.81</t>
+          <t>12990862.3932813</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>15182374.0361702</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>97.44</t>
+          <t>17398629.7431671</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>94.88</t>
+          <t>13525729.2168622</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>1369210838533.31</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>60.98</t>
+          <t>1398211155481.77</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>1302965570884.27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>1376346018122.06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>59.35</t>
+          <t>1507308857541.56</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>1734581670363.46</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>1785088374638.6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>1857637169936.97</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>2059681617472.02</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>62.33</t>
+          <t>2321696524820.56</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>62.29</t>
+          <t>2456210286506.51</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>2587375784087.85</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>72.07</t>
+          <t>2675433981116.65</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>2788230601765.88</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>2372345261103.38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>5508610.12112343</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>5779500.38561317</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>5835243.83024285</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>5825939.74977636</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>6156193.03397744</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>6918403.94604327</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>6759373.98424006</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>7066389.67821914</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>8247724.71966098</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>10000629.7768033</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>11347033.5735735</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>12990862.3932813</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>15182374.0361702</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>17398629.7431671</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>13525729.2168622</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10187069.843</t>
+          <t>1369210838533.31</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10526487.518</t>
+          <t>1398211155481.77</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10763913.125</t>
+          <t>1302965570884.27</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10904308.024</t>
+          <t>1376346018122.06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11114778.375</t>
+          <t>1507308857541.56</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11557854.987</t>
+          <t>1734581670363.46</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12096516.402</t>
+          <t>1785088374638.6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>12421661.693</t>
+          <t>1857637169936.97</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>12997272.164</t>
+          <t>2059681617472.02</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>13579443.376</t>
+          <t>2321696524820.56</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13858556.302</t>
+          <t>2456210286506.51</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>14148892.617</t>
+          <t>2587375784087.85</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>14462360.959</t>
+          <t>2675433981116.65</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>14982510.333</t>
+          <t>2788230601765.88</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>15186998.626</t>
+          <t>2372345261103.38</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5612489.778</t>
+          <t>-5.6843418860808e-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5793907.255</t>
+          <t>3.62661012331955e-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5950575.27</t>
+          <t>-3.21165316563565e-11</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6040066.365</t>
+          <t>-3.78577169612981e-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6181827.089</t>
+          <t>1.46940237755189e-11</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6430288.059</t>
+          <t>-7.40669747756328e-11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6688212.613</t>
+          <t>-4.2774672692758e-11</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6857814.678</t>
+          <t>-8.15134626463987e-11</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7128505.247</t>
+          <t>-4.30873114964925e-11</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7458458.734</t>
+          <t>-1.22213350550737e-11</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7636880.653</t>
+          <t>-1.67176494869636e-10</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7846160.34</t>
+          <t>1.92756033357e-10</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>8057390.774</t>
+          <t>-6.82121026329696e-13</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>8333370.878</t>
+          <t>-1.65414348884951e-11</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>8426342.408</t>
+          <t>-7.95239429862704e-11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12650256.647</t>
+          <t>1.99675559997559e-05</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13004972.066</t>
+          <t>-4.79817390441895e-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13232813.204</t>
+          <t>3.1590461730957e-05</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>13270629.119</t>
+          <t>-2.53915786743164e-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13377628.969</t>
+          <t>1.62720680236816e-05</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13874594.383</t>
+          <t>-1.71661376953125e-05</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14237586.366</t>
+          <t>-5.30481338500977e-05</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14538115.763</t>
+          <t>8.15987586975098e-05</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>15311439.532</t>
+          <t>-5.96046447753906e-05</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>16010068.821</t>
+          <t>-6.44326210021973e-05</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>16545559.338</t>
+          <t>-5.42402267456055e-05</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>17423487.366</t>
+          <t>2.50339508056641e-05</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>17724434.091</t>
+          <t>2.40802764892578e-05</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>18211445.182</t>
+          <t>2.76565551757812e-05</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>18317903.681</t>
+          <t>-2.74181365966797e-05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>13044696.2493569</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>13290445.6572976</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>13109990.0098204</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>12744920.4409387</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>13099043.7183165</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>13472403.0542317</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>13139352.6461774</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>13610791.9504054</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>15302508.5889529</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>17477377.8788738</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>19036366.4925341</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>20789014.6159227</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>23566423.5210953</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>26482309.9296852</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>24546496.3928784</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6892593.176</t>
+          <t>0.0304238278409743</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7065663.187</t>
+          <t>0.0321717035765016</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7192711.182</t>
+          <t>0.0356271734171024</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>7269378.67</t>
+          <t>0.0372549303996293</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7385203.603</t>
+          <t>0.0387343770573523</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7693319.45</t>
+          <t>0.0407372337988422</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7945250.166</t>
+          <t>0.0418532770966377</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8127108.809</t>
+          <t>0.0463244793865893</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8468085.877</t>
+          <t>0.0470084313685068</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8808176.354</t>
+          <t>0.049781213429953</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8999724.686</t>
+          <t>0.0518732544549356</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>9300699.611</t>
+          <t>0.0547611702957098</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>9450913.673</t>
+          <t>0.0564493898568859</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>9780263.088</t>
+          <t>0.119295067164386</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>9896808.776</t>
+          <t>0.113208822600823</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>30.067</t>
+          <t>15221384.2665545</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>30.727</t>
+          <t>15429141.5996516</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>30.764</t>
+          <t>15318515.8241342</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30.709</t>
+          <t>15330655.2517422</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>32.188</t>
+          <t>15900170.5237955</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>33.723</t>
+          <t>16434756.3332771</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>33.596</t>
+          <t>16415915.2920473</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>34.807</t>
+          <t>16947272.3259557</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>18854816.2148648</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>43.806</t>
+          <t>20892271.5702224</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>47.608</t>
+          <t>22393234.0699656</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>51.207</t>
+          <t>24078135.639353</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>58.332</t>
+          <t>26916296.3842254</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>65.943</t>
+          <t>29800411.7686462</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>61.677</t>
+          <t>28449891.2350189</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3763194.167</t>
+          <t>17578474.7456917</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3749544.115</t>
+          <t>17825902.783292</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3795961.601</t>
+          <t>17622048.5379238</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3853920.145</t>
+          <t>17525832.2310874</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3933919.494</t>
+          <t>18138832.5877258</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4149537.481</t>
+          <t>18642809.0924923</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4281703.68</t>
+          <t>18570731.973493</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4340942.504</t>
+          <t>19189505.8865293</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4510801.759</t>
+          <t>21446239.521659</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4642986.001</t>
+          <t>23767828.4082607</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>4763031.699</t>
+          <t>25436229.899039</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4867400.419</t>
+          <t>27318447.7177424</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4761877.896</t>
+          <t>30664014.807903</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>4881306.754</t>
+          <t>33890653.6721761</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4886466.877</t>
+          <t>32313568.4454114</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>96778054.8946727</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>96784030.5238092</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>93417153.378709</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>91398232.472819</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>93050073.1204685</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>54.96</t>
+          <t>93252101.2622381</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>91585051.8448396</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>94371503.0139495</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>105628209.099678</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>60.64</t>
+          <t>117888168.432761</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>60.34</t>
+          <t>125897169.697855</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>133119793.668559</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>69.21</t>
+          <t>146410390.501571</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>70.72</t>
+          <t>104856160.996644</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>72.44</t>
+          <t>102579524.861984</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>384.178</t>
+          <t>15665921.4860808</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>353.776</t>
+          <t>16039978.5631301</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>340.953</t>
+          <t>16510042.2759255</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>364.443</t>
+          <t>16876192.8435332</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>368.118</t>
+          <t>17406445.7421802</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>353.339</t>
+          <t>18206570.9093391</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>346.065</t>
+          <t>18582323.4643653</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>324.181</t>
+          <t>18756366.7829286</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>286.518</t>
+          <t>19172979.4482314</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>255.652</t>
+          <t>19672619.8776844</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>227.54</t>
+          <t>20299938.7554035</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>202.569</t>
+          <t>21058202.0944712</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>170.301</t>
+          <t>21888974.336494</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>152.775</t>
+          <t>22297839.3819118</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>162.281</t>
+          <t>21620809.2690694</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>13565284.4902116</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>13894479.1788083</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>14326217.1663642</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>14685191.1371901</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>15181063.4012884</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>15966041.3616605</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16339719.4160127</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>16492308.1631464</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>16849096.0929236</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>17328302.2869505</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>17894563.2368623</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>18608550.2435116</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>19310889.6876018</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>19686967.7166958</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>19023516.1251283</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>9727006.21110924</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>10035276.9766688</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10128112.3114608</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10077427.7870119</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10526162.8376043</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>10896360.2025556</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10791064.6552599</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11448476.5559995</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>12816830.7228595</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>14576107.0525679</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>15824326.0261009</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>17135010.161368</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>19250418.998403</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>21004228.4289976</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>19975907.9550105</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5612489778017.99</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5793907255123.12</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5950575270342.24</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6040066364708.29</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>6181827088534.49</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6430288059382.79</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6688212612842.19</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6857814677982.02</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7128505247247.53</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>7458458734041.13</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7636880652971.65</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7846160339939.15</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>8057390773660.85</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>8333370877641.31</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>8426342407614.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10187069843008</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10526487517611.5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10763913124639.8</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10904308023843</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>11114778375256.2</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>11557854986576.5</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12096516402073.1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>12421661692694.7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>12997272163552.3</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>13579443375836.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>13858556302351.8</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>14148892617089.6</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>14462360958833</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>14982510332742.5</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>15186998626007.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6892593175962.05</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>7065663186694.99</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>7192711182033.72</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>7269378670237.37</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>7385203603434.81</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>7693319449984.54</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7945250166345.18</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>8127108808534.68</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>8468085876564.43</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>8808176354371.52</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>8999724685725.04</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>9300699611373.29</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>9450913673174.63</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>9780263088274.59</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>9896808775656.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2660653299.68762</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2706543192.85967</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2747776983.70739</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2779312648.15922</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2813909726.61036</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2881293416.35052</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2937735363.00629</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2954355370.71242</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3027325963.39827</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3086349111.90897</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3143523990.29364</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3193889272.41759</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3225065864.56672</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3270744373.24015</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3280621015.7904</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1340302130.8872</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1366883339.16507</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1397427297.99206</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1415445994.83251</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1441207283.56612</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1481326410.23864</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1514240307.893</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1528087049.69162</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1560786843.92461</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1599028460.13363</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1636235991.91798</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1673184987.3684</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1700913042.44847</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1735034078.36997</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1740403487.76738</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5050806142338.25</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5155267839757.84</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5214922674001.2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5240263706642.2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5294293575380.68</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5443795235834.71</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5634934235581.34</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5731499925857.87</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5933322874864.6</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6103273607955.89</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6167087163760.7</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6238229391165.57</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6308545274711.33</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6459964683502.91</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6489569767236.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2540163194653.01</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2598384755765.98</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2647332326955.5</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2665359154981.25</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2706491456051.62</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2788332153999.34</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2876310616768.06</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2925557022779.32</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3011822532126.05</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3110191476674.07</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3156833450686.65</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3215874427204.57</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3270922465937.15</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3356370108232.97</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3371243035286.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.228898648427933</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.231919837016752</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.233019160662987</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.235284951021892</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.240991356161571</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.247797250380012</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.249827856813299</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.256671032957441</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.249986894033455</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.274989880290778</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.282125256882255</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.287263989153529</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.289429468407217</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.297021226523762</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.306401074424642</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.453619150842876</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.458991502302581</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.463130386661843</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.465589634981445</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.471018569897122</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.471636483388593</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.473224520750676</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.47349384372661</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.460707877633889</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.472300993256089</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.470266756125835</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.469502423185547</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.466965109699573</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.464136590079048</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.463349681517467</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.311210423639795</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.302816883592597</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.297578675591064</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.292853636915592</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.281718296863938</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.274294489159972</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.270675845366228</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.263563346248278</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.283033451269207</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.246437349393838</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.241336209934075</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.236961810604399</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.237333644837161</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.232570406340265</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.223977466996279</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.335405028268111</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.338411136515854</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.339669704236783</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.341902289518561</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.346903533136329</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.352299549381363</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.356278330181676</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.365145077653606</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.373805487600321</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.386008543030156</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.393178355201567</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.398494066586867</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.40454560307515</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.414310993611769</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.425707442136482</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.463667964044721</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.466754028426433</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.468371309821971</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.468343276562881</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.471208454264456</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.471064679839769</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.47013320487999</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.466470782425614</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.464642704475651</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.459175681330757</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.456677283528056</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.454664515077834</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.450251726895401</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.445197470725994</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.440419253199192</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.194655230683684</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.188563058054229</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.185687208937762</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.183482656915073</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.175616235595731</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.170363993775383</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.16731668793485</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.162112362917296</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.155280030920543</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.148543998635603</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.143872584266893</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.140569641331814</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.138930893025965</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.134219758658753</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.127601527660842</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>55182308.5366997</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>56556389.0503581</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>56598550.2992956</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>56060688.4328248</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>58306395.8341117</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>60817361.9019018</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>60202725.9733039</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>62263778.5854962</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>70209291.8668545</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>79623724.2735859</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>87525633.878685</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>95929115.303749</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>109397506.893586</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>122789481.799157</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>114158105.32809</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>28492989.6170379</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>29146972.6201288</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>29078015.2833797</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>28868950.3097123</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>29949423.6708065</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>30886319.2747992</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>30695232.7155385</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>31978700.6609161</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>35758542.8815301</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>40119766.8033391</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>43347211.2731476</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>46869212.7940502</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>52756188.9207813</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>58371735.6131579</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>55504275.79824</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4793954964.39064</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4967233143.90693</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5143827952.05915</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5218861965.06316</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>5277015495.56734</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>5365828710.33491</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5457821230.57687</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5565008351.87191</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5670797423.00182</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5798409794.11186</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5943544186.73891</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>6092466572.53306</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>6255830382.90053</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>6332877240.97938</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>6470859610.00551</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
